--- a/tests/fixtures/18_billing_statement/data-export-control.xlsx
+++ b/tests/fixtures/18_billing_statement/data-export-control.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -618,297 +618,298 @@
       <c r="I5" s="2" t="n"/>
       <c r="J5" s="2" t="n"/>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>table:</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>HEADER</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>line.date</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>line.type</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>line.invoice</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>line.description</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>line.amount</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>line.payment</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>line.balance</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="6" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="D8" s="7" t="n">
         <v>46054</v>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>product-15</t>
         </is>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F8" s="5" t="n">
         <v>415</v>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>product-15</t>
         </is>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H8" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="5" t="n">
+      <c r="I8" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="J7" s="5" t="n">
+      <c r="J8" s="5" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="8" t="n"/>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="9" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="8" t="n"/>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D9" s="10" t="n">
         <v>46056</v>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>product-16</t>
         </is>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="F9" s="8" t="n">
         <v>416</v>
       </c>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>product-16</t>
         </is>
       </c>
-      <c r="H8" s="8" t="n">
+      <c r="H9" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="I8" s="8" t="n">
+      <c r="I9" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="J8" s="8" t="n">
+      <c r="J9" s="8" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="6" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D9" s="7" t="n">
+      <c r="D10" s="7" t="n">
         <v>46058</v>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>product-17</t>
         </is>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F10" s="5" t="n">
         <v>417</v>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>product-17</t>
         </is>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="H10" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="I9" s="5" t="n">
+      <c r="I10" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="J9" s="5" t="n">
+      <c r="J10" s="5" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="8" t="n"/>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="9" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="8" t="n"/>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D11" s="10" t="n">
         <v>46060</v>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>product-18</t>
         </is>
       </c>
-      <c r="F10" s="8" t="n">
+      <c r="F11" s="8" t="n">
         <v>418</v>
       </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>product-18</t>
         </is>
       </c>
-      <c r="H10" s="8" t="n">
+      <c r="H11" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="I10" s="8" t="n">
+      <c r="I11" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="J10" s="8" t="n">
+      <c r="J11" s="8" t="n">
         <v>500</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D12" s="7" t="n">
         <v>46062</v>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>product-19</t>
         </is>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="F12" s="5" t="n">
         <v>419</v>
       </c>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n">
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="8" t="n"/>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="9" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="8" t="n"/>
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
-      <c r="H12" s="8" t="n"/>
-      <c r="I12" s="8" t="n"/>
-      <c r="J12" s="8" t="n">
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="8" t="n"/>
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="8" t="n"/>
+      <c r="J13" s="8" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="6" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="5" t="n"/>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve"> Total </t>
         </is>
       </c>
-      <c r="J13" s="5" t="n">
+      <c r="J14" s="5" t="n">
         <v>555</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="8" t="n"/>
-      <c r="B14" s="8" t="n"/>
-      <c r="C14" s="9" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="8" t="n"/>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>Reminder: Please include the statement number on your check.</t>
         </is>
       </c>
-      <c r="E14" s="8" t="n"/>
-      <c r="F14" s="8" t="n"/>
-      <c r="G14" s="8" t="n"/>
-      <c r="H14" s="8" t="n"/>
-      <c r="I14" s="8" t="n"/>
-      <c r="J14" s="8" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="8" t="n"/>
+      <c r="G15" s="8" t="n"/>
+      <c r="H15" s="8" t="n"/>
+      <c r="I15" s="8" t="n"/>
+      <c r="J15" s="8" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Terms: Balance due in 30 days.</t>
         </is>
       </c>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
